--- a/Downloads/Splitflask-Financials/handoff/CPA_TJ/CB_2024_Amendment_Packet.xlsx
+++ b/Downloads/Splitflask-Financials/handoff/CPA_TJ/CB_2024_Amendment_Packet.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,6 +72,10 @@
     <font/>
     <font>
       <i val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
     </font>
   </fonts>
   <fills count="14">
@@ -166,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -237,6 +241,7 @@
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -602,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -612,233 +617,251 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>⚠️ V2 CORRECTIONS APPLIED 2026-07-11 — CB 2024 — Schedule C | FINAL AMENDED NET: +$31,214</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="34" t="inlineStr">
+        <is>
+          <t>These corrections supersede the figures in the body of this sheet. Use AMENDED NET from row below for filing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Old Value</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Corrected Value</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AMENDED NET INCOME (FINAL)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>+$27,514 (Assembly 2C — had erroneous ~$3,700 Shopify Capital)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>+$31,214</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Remove the ~$3,700 Shopify Capital financing cost that was mistakenly assigned to CB. The advance is SGM's (bank descriptor: 'Shopify Capital ACH Debit — SOCIAL GEAR MEDIA'). CB deducts $0 from this advance. +$27,514 + $3,700 = +$31,214.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Shopify Capital financing cost — REMOVE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>~$3,700 ESTIMATE deducted on CB</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>$0 (REMOVE)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>The Shopify Capital advance ($41K / $5,330 finance charge) is SGM's debt, not CB's. CB serviced SGM's debt from CB store payouts (17% withholding) but CB is NOT the borrower. Remove from CB deductions. Note: this may create an interco receivable CB→SGM for amounts CB serviced; TJ determines.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>COGS note (method sensitivity)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Inventory method: $24,254.64 (591 units × $41.04)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>KEEP if inventory method elected; $0 if cash method kept</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CRITICAL: ALL entities filed CASH method. Under cash: 2023-paid Kangdao inventory deducts in 2023, NOT 2024. If TJ keeps cash method, CB 2024 COGS = ~$0 (or only 2024-paid costs), CB 2024 profit rises to ~+$55,468 BUT CB 2023 gets new $24,254 deduction. TJ must make method election FIRST (Step 1 of V2 Action Plan).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cross-packet tie F1 — VERIFY</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SGM receivable = CB payable: $8,135.50</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BOTH SIDES MUST MATCH</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SGM 2024 interco receivable $8,135.50 = CB 2024 interco payable $8,135.50. Verify both packets agree to the penny before filing either. (F4 freight also: $65,918 + $23,202.50 = $89,120.50 gross.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Shopify Capital — TJ interco note</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TJ: did CB service SGM's Shopify Capital debt from CB store payouts?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>If CB payouts had 17% Shopify Capital withholding routing to SGM's account, this is an interco receivable CB→SGM. TJ identifies and records if applicable. Does NOT change CB's P&amp;L deduction ($0 from this advance).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>--- END V2 CORRECTIONS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>CB 2024 (Schedule C) Amendment — Summary</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Cyberbrands LLC  |  EIN …7466  |  WF …5090  |  2024 filing period  |  ASSEMBLY 2B — COGS corrected; TJ/Bob to finalize</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Schedule C on personal Form 1040 (joint Arizechukwu &amp; Cheryl Nwosu).  Cyberbackpack product only — NOT Splitflask.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Line Item</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>As Filed
 (Schedule C)</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Amended
 (Bank+Platform basis)</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Source / Note</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>REVENUE</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Gross receipts as filed (TJ/Bob to supply from original Schedule C)</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C16" s="6" t="n">
         <v>107112.61</v>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>As-filed figure not available in source docs — TJ to confirm from 2024 personal return. Amended = $107,112.61 (bank + platform, post-BNPL correction). LOCKED.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  — Shopify CB store (bank deposits, net-of-Shopify-fees)</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C17" s="7" t="n">
         <v>80115.57000000001</v>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>S140-S151 (CB WF …5090, all 12 months footed). 1099-K for this channel is on SGM TIN ($82,263.58 S058) — not CB TIN; no CB 1099-K matching exposure for this channel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  — Amazon CB (bank deposits, net-of-fees)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>14467.4</v>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>S140-S151. 1099-K on CB TIN …7466: $22,414.83 (S053). Bank deposits $14,467 &lt; 1099-K $22,415 → gross-up $7,948 with matching fees (see 1099-K Recon tab). LOCKED.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  — TikTok CB (bank deposits)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>3624.91</v>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>S140-S151. No CB TikTok 1099-K issued. Below threshold or payer TIN differs. Bank-substantiated; non-1099-K channel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  — Wholesale (domestic + international / no 1099-K)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="n">
-        <v>8183.97</v>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>S140-S151. T Sportline (domestic) + Tobayama/Wise wires (Japan intl). Wholesale/intl exempt from 1099-K.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  — Marketplace (Walmart)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>716.76</v>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>S140-S151. Walmart Marketplace payouts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ⚠️  Channel detail sum</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="n">
-        <v>107108.61</v>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>⚠️  $107,108.61 = sum of 5 channels above. $4.00 delta vs locked $107,112.61. Likely minor miscellaneous item in bank; TJ confirm. Locked total = $107,112.61.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ✗ BNPL removed (Affirm / Klarna / Afterpay — double-count correction)</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>-9448.57</v>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>BNPL ran through Shopify CB; already captured inside Shopify deposits + Shopify 1099-K. Separate REV_BNPL_* bank entries are double-counts. REMOVED. Owner confirmed. LOCKED.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>AMENDED GROSS RECEIPTS (locked)</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="n">
-        <v>107112.61</v>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>LOCKED — $107,112.61. Above 1099-K floor $104,678.41. See 1099-K Recon tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>DEDUCTIONS</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Advertising (bank-substantiated)</t>
+          <t xml:space="preserve">  — Amazon CB (bank deposits, net-of-fees)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -847,33 +870,38 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>20276.87</v>
+        <v>14467.4</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>S140-S151. Incl. card ···5130 (CB WF debit = CB card). Meta $16,048.98, Google $779.75, Pinterest $289.10, TikTok $375.17, Social $55.47, ADS mix $2,728.35. SOURCED.</t>
+          <t>S140-S151. 1099-K on CB TIN …7466: $22,414.83 (S053). Bank deposits $14,467 &lt; 1099-K $22,415 → gross-up $7,948 with matching fees (see 1099-K Recon tab). LOCKED.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ✓ Card ···5130 confirmed CB card (not SGM)</t>
+          <t xml:space="preserve">  — TikTok CB (bank deposits)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>?</t>
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>7873.38</v>
+        <v>3624.91</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>···5130 = Cyberbrands WF debit card. $7,873.38 CB 2024 Facebook charges on this card. Within the $20,276.87 total above (not additive). Source: S140-S151 + 2024 FB invoice (S344 analog).</t>
+          <t>S140-S151. No CB TikTok 1099-K issued. Below threshold or payer TIN differs. Bank-substantiated; non-1099-K channel.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ✅ COGS — inventory method (CORRECTED, Assembly 2B)</t>
+          <t xml:space="preserve">  — Wholesale (domestic + international / no 1099-K)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -882,18 +910,18 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>24254.64</v>
+        <v>8183.97</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>591 units × $41.04 per-unit Kangdao landed cost = $24,254.64. Inventory/accrual method. Replaces bank-sourced $4,178.29. ⚠️ TJ: must be consistent with SGM 2024 method; 2023 Kangdao payments NOT to be deducted on 2023 return.</t>
+          <t>S140-S151. T Sportline (domestic) + Tobayama/Wise wires (Japan intl). Wholesale/intl exempt from 1099-K.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Freight — Cyberbackpack share (Path b — LOCKED owner decision)</t>
+          <t xml:space="preserve">  — Marketplace (Walmart)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -902,154 +930,284 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>23202.5</v>
+        <v>716.76</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>LOCKED (Path b). $15,067 direct CB payments (S140 Jan $12,067 + S144 May $2,000 + S145 Jun $1,000) + $8,135.50 interco payable to SGM (CB's unpaid share of SGM-fronted CB shipment). CB deducts full $23,202.50. MATCHES SGM 2024 packet ($65,918 net). See Intercompany tab.</t>
+          <t>S140-S151. Walmart Marketplace payouts.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">  ⚠️  Channel detail sum</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>107108.61</v>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>⚠️  $107,108.61 = sum of 5 channels above. $4.00 delta vs locked $107,112.61. Likely minor miscellaneous item in bank; TJ confirm. Locked total = $107,112.61.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ✗ BNPL removed (Affirm / Klarna / Afterpay — double-count correction)</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>-9448.57</v>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>BNPL ran through Shopify CB; already captured inside Shopify deposits + Shopify 1099-K. Separate REV_BNPL_* bank entries are double-counts. REMOVED. Owner confirmed. LOCKED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>AMENDED GROSS RECEIPTS (locked)</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>107112.61</v>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>LOCKED — $107,112.61. Above 1099-K floor $104,678.41. See 1099-K Recon tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>DEDUCTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Advertising (bank-substantiated)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>20276.87</v>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>S140-S151. Incl. card ···5130 (CB WF debit = CB card). Meta $16,048.98, Google $779.75, Pinterest $289.10, TikTok $375.17, Social $55.47, ADS mix $2,728.35. SOURCED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ✓ Card ···5130 confirmed CB card (not SGM)</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>7873.38</v>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>···5130 = Cyberbrands WF debit card. $7,873.38 CB 2024 Facebook charges on this card. Within the $20,276.87 total above (not additive). Source: S140-S151 + 2024 FB invoice (S344 analog).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ✅ COGS — inventory method (CORRECTED, Assembly 2B)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>24254.64</v>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>591 units × $41.04 per-unit Kangdao landed cost = $24,254.64. Inventory/accrual method. Replaces bank-sourced $4,178.29. ⚠️ TJ: must be consistent with SGM 2024 method; 2023 Kangdao payments NOT to be deducted on 2023 return.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Freight — Cyberbackpack share (Path b — LOCKED owner decision)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>23202.5</v>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>LOCKED (Path b). $15,067 direct CB payments (S140 Jan $12,067 + S144 May $2,000 + S145 Jun $1,000) + $8,135.50 interco payable to SGM (CB's unpaid share of SGM-fronted CB shipment). CB deducts full $23,202.50. MATCHES SGM 2024 packet ($65,918 net). See Intercompany tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">  OPEX (bank-substantiated)</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C31" s="7" t="n">
         <v>8164.18</v>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>S140-S151. Software $5,117.44, Travel $1,345.52, Supplies $952.57, Meals $242.12, Bank fees $140.81, Shipping $83.33, Platform fees $133.76, Contract labor $68.30, Freelance $55.25, Auto $20.00, Other $5.08. TJ: travel/meals documentation.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>TOTAL DEDUCTIONS</t>
         </is>
       </c>
-      <c r="C23" s="13" t="n">
+      <c r="C32" s="13" t="n">
         <v>75898.19</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>$20,276.87 ads + $24,254.64 COGS (corrected) + $23,202.50 freight + $8,164.18 OPEX = $75,898.19. COGS corrected from $4,178.29 to $24,254.64 (+$20,076.35). Platform fees are gross-up washes (see Deductions tab) — NOT in this total.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>NET SCHEDULE C INCOME (amended)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>As-filed net income (TJ/Bob to supply)</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>TJ: provide from 2024 personal Schedule C.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>Amended gross receipts</t>
         </is>
       </c>
-      <c r="C27" s="15" t="n">
+      <c r="C36" s="15" t="n">
         <v>107112.61</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>Less: total deductions</t>
         </is>
       </c>
-      <c r="C28" s="15" t="n">
+      <c r="C37" s="15" t="n">
         <v>-75898.19</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>All sourced; see Deductions tab. COGS corrected (Assembly 2B).</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>AMENDED NET SCHEDULE C INCOME</t>
         </is>
       </c>
-      <c r="C29" s="10" t="n">
+      <c r="C38" s="10" t="n">
         <v>27514.42</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D38" s="11">
         <f> $107,112.61 gross receipts − $79,598.19 total deductions = $27,514.42. ASSEMBLY 2C UPDATE: Shopify Capital financing cost $3,700 (ESTIMATE) added as deduction. Previously $31,214.42 (ASSEMBLY 2B); now $27,514.42 (−$3,700). Direction still FAVORABLE. Estimate to be confirmed with Shopify Capital agreement.</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>VERDICT</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C40" s="16" t="inlineStr">
         <is>
           <t>✅ FAVORABLE (CORRECTED)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Amendment FAVORABLE. Net Sch C $27,514.42 (profit, down from $31,214.42 after Shopify Capital financing cost $3,700 ESTIMATE). All deductions bank-substantiated or estimated-from-source. COGS corrected to inventory method $24,254.64. Shopify Capital financing cost added $3,700 (ESTIMATE — confirm with agreement). Pending TJ items: Shopify Capital exact financing cost; ad/mgmt interco ($2,559 + $6,000). Does not raise tax vs any reasonable as-filed basis.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>⚠️  CROSS-PACKET DEPENDENCY</t>
         </is>
       </c>
-      <c r="D32" s="18" t="inlineStr">
+      <c r="D41" s="18" t="inlineStr">
         <is>
           <t>The $8,135.50 interco payable (CB) MUST match the $8,135.50 interco receivable in SGM 2024 Amendment Packet. These are the same dollar — same CB shipment. Both packets must agree before filing either.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>⚠️  SCOPE NOTE</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>CYBERBACKPACK ONLY — this packet is for the Cyberbrands Schedule C. Splitflask revenue is EXCLUDED. Kendra Scott due diligence uses Splitflask GMV ($751,891) — no Cyberbackpack in the deal universe.</t>
         </is>
@@ -1800,7 +1958,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -1850,7 +2007,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
@@ -1978,7 +2134,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
@@ -2045,7 +2200,6 @@
         <v/>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="20" t="inlineStr">
         <is>
@@ -2293,7 +2447,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" s="20" t="inlineStr">
         <is>
@@ -2421,7 +2574,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
